--- a/data/trans_orig/P42B-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P42B-Clase-trans_orig.xlsx
@@ -907,12 +907,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57547</t>
+          <t>57542</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72494</t>
+          <t>72033</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -922,12 +922,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -942,12 +942,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57547</t>
+          <t>57542</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72494</t>
+          <t>72033</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,03%</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11727</t>
+          <t>11724</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1020,12 +1020,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11727</t>
+          <t>11724</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1063,12 +1063,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6561</t>
+          <t>6998</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20089</t>
+          <t>19825</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6561</t>
+          <t>6998</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20089</t>
+          <t>19825</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1113,12 +1113,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>23,95%</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4667</t>
+          <t>5588</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4667</t>
+          <t>5588</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6981</t>
+          <t>6688</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6981</t>
+          <t>6688</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61458</t>
+          <t>60935</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>75568</t>
+          <t>75246</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1472,12 +1472,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1492,12 +1492,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>61458</t>
+          <t>60935</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>75568</t>
+          <t>75246</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1507,12 +1507,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,58%</t>
         </is>
       </c>
     </row>
@@ -1535,12 +1535,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>948</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10512</t>
+          <t>10765</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1550,12 +1550,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>948</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10512</t>
+          <t>10765</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4209</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>15427</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1628,12 +1628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1648,12 +1648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4209</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>15427</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1663,12 +1663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6154</t>
+          <t>6972</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6154</t>
+          <t>6972</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>22,01%</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5856</t>
+          <t>5446</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5856</t>
+          <t>5446</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>17,2%</t>
         </is>
       </c>
     </row>
@@ -2007,12 +2007,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16473</t>
+          <t>15858</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26490</t>
+          <t>26507</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2042,12 +2042,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>16473</t>
+          <t>15858</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>26490</t>
+          <t>26507</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2057,12 +2057,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,7%</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4822</t>
+          <t>4639</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4822</t>
+          <t>4639</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,65%</t>
         </is>
       </c>
     </row>
@@ -2163,12 +2163,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>10112</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2178,12 +2178,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>10112</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2213,12 +2213,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>31,93%</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5427</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5427</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -2401,12 +2401,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>978</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9666</t>
+          <t>9759</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2436,12 +2436,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>978</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9666</t>
+          <t>9759</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -2479,12 +2479,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2678</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>12736</t>
+          <t>12766</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2678</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>12736</t>
+          <t>12766</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>92217</t>
+          <t>92912</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>114722</t>
+          <t>114182</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>92217</t>
+          <t>92912</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>114722</t>
+          <t>114182</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,15%</t>
         </is>
       </c>
     </row>
@@ -2635,12 +2635,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12086</t>
+          <t>12359</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2650,12 +2650,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2670,12 +2670,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12086</t>
+          <t>12359</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -2713,12 +2713,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22838</t>
+          <t>22659</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>43351</t>
+          <t>40884</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>22838</t>
+          <t>22659</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>43351</t>
+          <t>40884</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>26,91%</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>6899</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>6899</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -3029,12 +3029,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4030</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>15663</t>
+          <t>16308</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>4030</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>15663</t>
+          <t>16308</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>
@@ -3107,12 +3107,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>66749</t>
+          <t>67501</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>87862</t>
+          <t>87749</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>66749</t>
+          <t>67501</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>87862</t>
+          <t>87749</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,6%</t>
         </is>
       </c>
     </row>
@@ -3185,12 +3185,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>3133</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>15948</t>
+          <t>16917</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>3133</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>15948</t>
+          <t>16917</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,96%</t>
         </is>
       </c>
     </row>
@@ -3263,12 +3263,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>9348</t>
+          <t>9339</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>24125</t>
+          <t>23536</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>9348</t>
+          <t>9339</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>24125</t>
+          <t>23536</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>20,81%</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>6437</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>6437</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -3501,12 +3501,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1764</t>
+          <t>1821</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>10261</t>
+          <t>10198</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1764</t>
+          <t>1821</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>10261</t>
+          <t>10198</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>6932</t>
+          <t>7056</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>20509</t>
+          <t>20971</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>6932</t>
+          <t>7056</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>20509</t>
+          <t>20971</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -3657,12 +3657,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>130939</t>
+          <t>132728</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>155756</t>
+          <t>155347</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -3692,12 +3692,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>130939</t>
+          <t>132728</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>155756</t>
+          <t>155347</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,71%</t>
         </is>
       </c>
     </row>
@@ -3735,12 +3735,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>2965</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>14917</t>
+          <t>14267</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2965</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>14917</t>
+          <t>14267</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,5%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>11560</t>
+          <t>11641</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>28815</t>
+          <t>28614</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>11560</t>
+          <t>11641</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>28815</t>
+          <t>28614</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,05%</t>
         </is>
       </c>
     </row>
@@ -3973,12 +3973,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>862</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>7530</t>
+          <t>7660</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>862</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>7530</t>
+          <t>7660</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>7790</t>
+          <t>8221</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>22494</t>
+          <t>23646</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>7790</t>
+          <t>8221</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>22494</t>
+          <t>23646</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -4129,12 +4129,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>21204</t>
+          <t>20494</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>42829</t>
+          <t>41821</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -4144,12 +4144,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>21204</t>
+          <t>20494</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>42829</t>
+          <t>41821</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -4207,12 +4207,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>461134</t>
+          <t>464762</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>505826</t>
+          <t>508328</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -4222,12 +4222,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>461134</t>
+          <t>464762</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>505826</t>
+          <t>508328</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4257,12 +4257,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>77,67%</t>
         </is>
       </c>
     </row>
@@ -4285,12 +4285,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>21815</t>
+          <t>21452</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>45467</t>
+          <t>43352</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -4300,12 +4300,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>21815</t>
+          <t>21452</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>45467</t>
+          <t>43352</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4335,12 +4335,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -4363,12 +4363,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>75341</t>
+          <t>75259</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>111201</t>
+          <t>110760</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -4378,12 +4378,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>75341</t>
+          <t>75259</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>111201</t>
+          <t>110760</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>
@@ -4696,12 +4696,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>939</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7868</t>
+          <t>7890</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4731,12 +4731,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>939</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7868</t>
+          <t>7890</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9186</t>
+          <t>9869</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9186</t>
+          <t>9869</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14047</t>
+          <t>13369</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14047</t>
+          <t>13369</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -4930,12 +4930,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>199693</t>
+          <t>198919</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>229935</t>
+          <t>229389</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4945,12 +4945,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4965,12 +4965,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>199693</t>
+          <t>198919</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>229935</t>
+          <t>229389</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4980,12 +4980,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,29%</t>
         </is>
       </c>
     </row>
@@ -5008,12 +5008,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9745</t>
+          <t>9682</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25856</t>
+          <t>26514</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5023,12 +5023,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5043,12 +5043,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9745</t>
+          <t>9682</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25856</t>
+          <t>26514</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5058,12 +5058,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -5086,12 +5086,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31045</t>
+          <t>29991</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>55232</t>
+          <t>55622</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5101,12 +5101,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31045</t>
+          <t>29991</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>55232</t>
+          <t>55622</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,47%</t>
         </is>
       </c>
     </row>
@@ -5246,12 +5246,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>972</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9435</t>
+          <t>9800</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5261,12 +5261,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>972</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9435</t>
+          <t>9800</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -5329,7 +5329,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7743</t>
+          <t>7741</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7743</t>
+          <t>7741</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5402,12 +5402,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10596</t>
+          <t>10159</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5437,12 +5437,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10596</t>
+          <t>10159</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -5480,12 +5480,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>214348</t>
+          <t>214170</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>240036</t>
+          <t>240904</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5515,12 +5515,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>214348</t>
+          <t>214170</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>240036</t>
+          <t>240904</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>85,32%</t>
         </is>
       </c>
     </row>
@@ -5558,12 +5558,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7116</t>
+          <t>7006</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22131</t>
+          <t>22545</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7116</t>
+          <t>7006</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22131</t>
+          <t>22545</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -5636,12 +5636,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20355</t>
+          <t>18731</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40869</t>
+          <t>40458</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5651,12 +5651,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20355</t>
+          <t>18731</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40869</t>
+          <t>40458</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5686,12 +5686,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6020</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6020</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4745</t>
+          <t>4348</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5914,7 +5914,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4745</t>
+          <t>4348</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -5952,12 +5952,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>925</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>8527</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>925</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>8527</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -6030,12 +6030,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>151652</t>
+          <t>152510</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>177580</t>
+          <t>179494</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>151652</t>
+          <t>152510</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>177580</t>
+          <t>179494</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6080,12 +6080,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>82,98%</t>
         </is>
       </c>
     </row>
@@ -6108,12 +6108,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4307</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18148</t>
+          <t>18035</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4307</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18148</t>
+          <t>18035</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23130</t>
+          <t>23646</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>46230</t>
+          <t>46036</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>23130</t>
+          <t>23646</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>46230</t>
+          <t>46036</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,28%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7992</t>
+          <t>8093</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23610</t>
+          <t>24299</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7992</t>
+          <t>8093</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23610</t>
+          <t>24299</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -6424,12 +6424,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>956</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8821</t>
+          <t>9476</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6459,12 +6459,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>956</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8821</t>
+          <t>9476</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -6502,12 +6502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4954</t>
+          <t>5040</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>19848</t>
+          <t>18509</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6517,12 +6517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6537,12 +6537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4954</t>
+          <t>5040</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>19848</t>
+          <t>18509</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6552,12 +6552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -6580,12 +6580,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>415385</t>
+          <t>417281</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>461256</t>
+          <t>464347</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6615,12 +6615,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>415385</t>
+          <t>417281</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>461256</t>
+          <t>464347</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6630,12 +6630,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,56%</t>
         </is>
       </c>
     </row>
@@ -6658,12 +6658,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>32690</t>
+          <t>34105</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>59557</t>
+          <t>59806</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6693,12 +6693,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>32690</t>
+          <t>34105</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>59557</t>
+          <t>59806</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -6736,12 +6736,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>82959</t>
+          <t>82878</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>122439</t>
+          <t>121530</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -6771,12 +6771,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>82959</t>
+          <t>82878</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>122439</t>
+          <t>121530</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -6786,12 +6786,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4280</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>18910</t>
+          <t>19008</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4280</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>18910</t>
+          <t>19008</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -6974,12 +6974,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>3879</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>16829</t>
+          <t>15616</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -6989,12 +6989,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7009,12 +7009,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>3879</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>16829</t>
+          <t>15616</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -7052,12 +7052,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>15688</t>
+          <t>15937</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -7087,12 +7087,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>15688</t>
+          <t>15937</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -7130,12 +7130,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>364047</t>
+          <t>365355</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>412757</t>
+          <t>411299</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -7145,12 +7145,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -7165,12 +7165,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>364047</t>
+          <t>365355</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>412757</t>
+          <t>411299</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>68,9%</t>
         </is>
       </c>
     </row>
@@ -7208,12 +7208,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>28353</t>
+          <t>27344</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>54000</t>
+          <t>53735</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -7223,12 +7223,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -7243,12 +7243,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>28353</t>
+          <t>27344</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>54000</t>
+          <t>53735</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -7258,12 +7258,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>121074</t>
+          <t>123862</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>165183</t>
+          <t>165177</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -7321,12 +7321,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>121074</t>
+          <t>123862</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>165183</t>
+          <t>165177</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -7426,7 +7426,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>5214</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>18438</t>
+          <t>18756</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>5214</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>18438</t>
+          <t>18756</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -7524,12 +7524,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>14574</t>
+          <t>13683</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -7559,12 +7559,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>14574</t>
+          <t>13683</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -7602,12 +7602,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>6253</t>
+          <t>7166</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>20723</t>
+          <t>21074</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>6253</t>
+          <t>7166</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>20723</t>
+          <t>21074</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>508972</t>
+          <t>509087</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>557557</t>
+          <t>559982</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>508972</t>
+          <t>509087</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>557557</t>
+          <t>559982</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,64%</t>
         </is>
       </c>
     </row>
@@ -7758,12 +7758,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>26761</t>
+          <t>25996</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>50242</t>
+          <t>49157</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -7793,12 +7793,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>26761</t>
+          <t>25996</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>50242</t>
+          <t>49157</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -7836,12 +7836,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>119088</t>
+          <t>118388</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>162276</t>
+          <t>161613</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -7851,12 +7851,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>119088</t>
+          <t>118388</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>162276</t>
+          <t>161613</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -7886,12 +7886,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>31040</t>
+          <t>29962</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>58888</t>
+          <t>59045</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>31040</t>
+          <t>29962</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>58888</t>
+          <t>59045</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -8046,12 +8046,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -8074,12 +8074,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>16395</t>
+          <t>15727</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>38069</t>
+          <t>36947</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -8089,12 +8089,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>16395</t>
+          <t>15727</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>38069</t>
+          <t>36947</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -8124,12 +8124,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -8157,7 +8157,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>58695</t>
+          <t>59800</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -8172,7 +8172,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -8192,7 +8192,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>58695</t>
+          <t>59800</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -8207,7 +8207,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -8230,12 +8230,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>1925790</t>
+          <t>1923291</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2021040</t>
+          <t>2021166</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -8245,7 +8245,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -8265,12 +8265,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>1925790</t>
+          <t>1923291</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>2021040</t>
+          <t>2021166</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -8280,7 +8280,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>136966</t>
+          <t>138735</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>186592</t>
+          <t>190413</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -8343,12 +8343,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>136966</t>
+          <t>138735</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>186592</t>
+          <t>190413</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -8358,12 +8358,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -8386,12 +8386,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>448367</t>
+          <t>452966</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>527798</t>
+          <t>530372</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -8401,12 +8401,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>448367</t>
+          <t>452966</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>527798</t>
+          <t>530372</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -8719,12 +8719,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3793</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14778</t>
+          <t>17025</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8754,12 +8754,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3793</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14778</t>
+          <t>17025</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -8875,12 +8875,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11164</t>
+          <t>10351</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8910,12 +8910,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11164</t>
+          <t>10351</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>229601</t>
+          <t>230948</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>259310</t>
+          <t>260356</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>229601</t>
+          <t>230948</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>259310</t>
+          <t>260356</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>84,14%</t>
         </is>
       </c>
     </row>
@@ -9031,12 +9031,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9385</t>
+          <t>8695</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25467</t>
+          <t>25232</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9046,12 +9046,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9385</t>
+          <t>8695</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25467</t>
+          <t>25232</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -9109,12 +9109,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22877</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>45583</t>
+          <t>46169</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9124,12 +9124,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22877</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45583</t>
+          <t>46169</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9159,12 +9159,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,92%</t>
         </is>
       </c>
     </row>
@@ -9269,12 +9269,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2693</t>
+          <t>2556</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13328</t>
+          <t>13413</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9284,12 +9284,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9304,12 +9304,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2693</t>
+          <t>2556</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13328</t>
+          <t>13413</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9319,12 +9319,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -9347,12 +9347,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>943</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8044</t>
+          <t>8768</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9382,12 +9382,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>943</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8044</t>
+          <t>8768</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -9425,12 +9425,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13807</t>
+          <t>13878</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9440,12 +9440,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9460,12 +9460,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13807</t>
+          <t>13878</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9475,12 +9475,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -9503,12 +9503,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>261050</t>
+          <t>261379</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>290060</t>
+          <t>290097</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9518,12 +9518,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>261050</t>
+          <t>261379</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>290060</t>
+          <t>290097</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9553,12 +9553,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,74%</t>
         </is>
       </c>
     </row>
@@ -9581,12 +9581,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>7355</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22815</t>
+          <t>22271</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9616,12 +9616,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>7355</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22815</t>
+          <t>22271</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9631,12 +9631,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -9659,12 +9659,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18811</t>
+          <t>18687</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41588</t>
+          <t>41056</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9694,12 +9694,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18811</t>
+          <t>18687</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41588</t>
+          <t>41056</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -9819,12 +9819,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9872</t>
+          <t>10378</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9854,12 +9854,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9872</t>
+          <t>10378</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9874,7 +9874,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -9980,7 +9980,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9569</t>
+          <t>9707</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9995,7 +9995,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10015,7 +10015,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9569</t>
+          <t>9707</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -10053,12 +10053,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>97471</t>
+          <t>95897</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>118162</t>
+          <t>118817</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10068,12 +10068,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10088,12 +10088,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>97471</t>
+          <t>95897</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>118162</t>
+          <t>118817</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10103,12 +10103,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>83,43%</t>
         </is>
       </c>
     </row>
@@ -10136,7 +10136,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9288</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10151,7 +10151,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10171,7 +10171,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9288</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -10209,12 +10209,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>16173</t>
+          <t>16427</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>35234</t>
+          <t>37409</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10224,12 +10224,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10244,12 +10244,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>16173</t>
+          <t>16427</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>35234</t>
+          <t>37409</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10259,12 +10259,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>26,27%</t>
         </is>
       </c>
     </row>
@@ -10369,12 +10369,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9850</t>
+          <t>9882</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>25630</t>
+          <t>26652</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10384,12 +10384,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9850</t>
+          <t>9882</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>25630</t>
+          <t>26652</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10419,12 +10419,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11671</t>
+          <t>11620</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10467,7 +10467,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10482,12 +10482,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11671</t>
+          <t>11620</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10502,7 +10502,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -10525,12 +10525,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8345</t>
+          <t>9068</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>24018</t>
+          <t>24692</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10540,12 +10540,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10560,12 +10560,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>8345</t>
+          <t>9068</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>24018</t>
+          <t>24692</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10575,12 +10575,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -10603,12 +10603,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>488702</t>
+          <t>487979</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>532800</t>
+          <t>536034</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10638,12 +10638,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>488702</t>
+          <t>487979</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>532800</t>
+          <t>536034</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10653,12 +10653,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>77,44%</t>
         </is>
       </c>
     </row>
@@ -10681,12 +10681,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>41329</t>
+          <t>41075</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>70209</t>
+          <t>67968</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>41329</t>
+          <t>41075</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>70209</t>
+          <t>67968</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -10759,12 +10759,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>72632</t>
+          <t>71088</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>106088</t>
+          <t>108225</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10774,12 +10774,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>72632</t>
+          <t>71088</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>106088</t>
+          <t>108225</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -10919,12 +10919,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>7528</t>
+          <t>7739</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>23487</t>
+          <t>23785</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10934,12 +10934,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10954,12 +10954,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7528</t>
+          <t>7739</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>23487</t>
+          <t>23785</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10969,12 +10969,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -10997,12 +10997,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>2209</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>13503</t>
+          <t>13620</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11012,12 +11012,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11032,12 +11032,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>2209</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>13503</t>
+          <t>13620</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11047,12 +11047,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -11075,12 +11075,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>11227</t>
+          <t>11538</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>30141</t>
+          <t>30381</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11110,12 +11110,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>11227</t>
+          <t>11538</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>30141</t>
+          <t>30381</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11125,12 +11125,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -11153,12 +11153,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>362148</t>
+          <t>363496</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>408725</t>
+          <t>408992</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -11188,12 +11188,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>362148</t>
+          <t>363496</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>408725</t>
+          <t>408992</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -11203,12 +11203,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,54%</t>
         </is>
       </c>
     </row>
@@ -11231,12 +11231,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>23587</t>
+          <t>23155</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>46306</t>
+          <t>46021</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>23587</t>
+          <t>23155</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>46306</t>
+          <t>46021</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -11309,12 +11309,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>85402</t>
+          <t>87144</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>123103</t>
+          <t>123171</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -11324,12 +11324,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -11344,12 +11344,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>85402</t>
+          <t>87144</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>123103</t>
+          <t>123171</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -11359,12 +11359,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,85%</t>
         </is>
       </c>
     </row>
@@ -11449,7 +11449,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -11469,12 +11469,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>13225</t>
+          <t>14506</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>33017</t>
+          <t>35508</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -11484,12 +11484,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -11504,12 +11504,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>13225</t>
+          <t>14506</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>33017</t>
+          <t>35508</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -11519,12 +11519,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -11552,7 +11552,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>4541</t>
+          <t>4869</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11567,7 +11567,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11587,7 +11587,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>4541</t>
+          <t>4869</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11602,7 +11602,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -11625,12 +11625,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>30287</t>
+          <t>28465</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>55683</t>
+          <t>54747</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11640,12 +11640,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11660,12 +11660,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>30287</t>
+          <t>28465</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>55683</t>
+          <t>54747</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11675,12 +11675,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -11703,12 +11703,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>515508</t>
+          <t>516587</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>566983</t>
+          <t>564028</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11718,12 +11718,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11738,12 +11738,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>515508</t>
+          <t>516587</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>566983</t>
+          <t>564028</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11753,12 +11753,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>77,56%</t>
         </is>
       </c>
     </row>
@@ -11781,12 +11781,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>16100</t>
+          <t>15946</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>35999</t>
+          <t>35079</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11796,12 +11796,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>16100</t>
+          <t>15946</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>35999</t>
+          <t>35079</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11831,12 +11831,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -11859,12 +11859,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>80168</t>
+          <t>81436</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>117747</t>
+          <t>118823</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11874,12 +11874,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>80168</t>
+          <t>81436</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>117747</t>
+          <t>118823</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11909,12 +11909,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -12019,12 +12019,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>55275</t>
+          <t>54527</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>90561</t>
+          <t>88612</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -12034,12 +12034,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -12054,12 +12054,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>55275</t>
+          <t>54527</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>90561</t>
+          <t>88612</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -12069,12 +12069,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -12097,12 +12097,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>8993</t>
+          <t>9141</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>24811</t>
+          <t>24700</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12112,12 +12112,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>8993</t>
+          <t>9141</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>24811</t>
+          <t>24700</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -12175,12 +12175,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>71268</t>
+          <t>71238</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>109680</t>
+          <t>111312</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12210,12 +12210,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>71268</t>
+          <t>71238</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>109680</t>
+          <t>111312</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12230,7 +12230,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>2022183</t>
+          <t>2021951</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2114012</t>
+          <t>2115400</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12268,12 +12268,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12288,12 +12288,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>2022183</t>
+          <t>2021951</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>2114012</t>
+          <t>2115400</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12303,12 +12303,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,38%</t>
         </is>
       </c>
     </row>
@@ -12331,12 +12331,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>123428</t>
+          <t>122840</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>170617</t>
+          <t>169586</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>123428</t>
+          <t>122840</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>170617</t>
+          <t>169586</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -12381,12 +12381,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -12409,12 +12409,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>346252</t>
+          <t>342603</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>419109</t>
+          <t>414832</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -12444,12 +12444,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>346252</t>
+          <t>342603</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>419109</t>
+          <t>414832</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,98%</t>
         </is>
       </c>
     </row>
@@ -12737,22 +12737,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9253</t>
+          <t>9889</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>5133</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15407</t>
+          <t>17175</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -12762,7 +12762,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -12772,22 +12772,22 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9253</t>
+          <t>9889</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>5133</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15407</t>
+          <t>17175</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -12797,7 +12797,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -12815,7 +12815,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -12825,12 +12825,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4813</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -12850,7 +12850,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -12860,12 +12860,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4813</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -12893,22 +12893,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2939</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6312</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -12928,22 +12928,22 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2939</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6312</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -12971,32 +12971,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>218116</t>
+          <t>238614</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>205686</t>
+          <t>224653</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>228738</t>
+          <t>249827</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13006,32 +13006,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>218116</t>
+          <t>238614</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>205686</t>
+          <t>224653</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>228738</t>
+          <t>249827</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,2%</t>
         </is>
       </c>
     </row>
@@ -13049,32 +13049,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>7074</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>3449</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12994</t>
+          <t>12964</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -13084,32 +13084,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>7074</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>3449</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12994</t>
+          <t>12964</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -13127,32 +13127,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33265</t>
+          <t>36439</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24603</t>
+          <t>27495</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>45134</t>
+          <t>49333</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -13162,32 +13162,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33265</t>
+          <t>36439</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24603</t>
+          <t>27495</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45134</t>
+          <t>49333</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,63%</t>
         </is>
       </c>
     </row>
@@ -13205,17 +13205,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>271946</t>
+          <t>296707</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>271946</t>
+          <t>296707</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>271946</t>
+          <t>296707</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -13240,17 +13240,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>271946</t>
+          <t>296707</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>271946</t>
+          <t>296707</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>271946</t>
+          <t>296707</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -13287,32 +13287,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11894</t>
+          <t>13200</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>7925</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19073</t>
+          <t>21561</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -13322,32 +13322,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11894</t>
+          <t>13200</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>7925</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19073</t>
+          <t>21561</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -13365,7 +13365,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -13375,12 +13375,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5415</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -13390,7 +13390,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -13400,7 +13400,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -13410,12 +13410,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5415</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -13425,7 +13425,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -13443,32 +13443,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4349</t>
+          <t>4542</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8060</t>
+          <t>8874</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -13478,32 +13478,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4349</t>
+          <t>4542</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8060</t>
+          <t>8874</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -13521,32 +13521,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>182655</t>
+          <t>202873</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>171314</t>
+          <t>189533</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>193992</t>
+          <t>214021</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -13556,32 +13556,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>182655</t>
+          <t>202873</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>171314</t>
+          <t>189533</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>193992</t>
+          <t>214021</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>81,42%</t>
         </is>
       </c>
     </row>
@@ -13599,32 +13599,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8381</t>
+          <t>9456</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4480</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14408</t>
+          <t>15259</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -13634,32 +13634,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8381</t>
+          <t>9456</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4480</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14408</t>
+          <t>15259</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -13677,32 +13677,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>25817</t>
+          <t>31246</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18137</t>
+          <t>22719</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36940</t>
+          <t>42599</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13712,32 +13712,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>25817</t>
+          <t>31246</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18137</t>
+          <t>22719</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36940</t>
+          <t>42599</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,21%</t>
         </is>
       </c>
     </row>
@@ -13755,17 +13755,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>234602</t>
+          <t>262848</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>234602</t>
+          <t>262848</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>234602</t>
+          <t>262848</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13790,17 +13790,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>234602</t>
+          <t>262848</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>234602</t>
+          <t>262848</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>234602</t>
+          <t>262848</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13837,32 +13837,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3909</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1766</t>
+          <t>2209</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8845</t>
+          <t>9272</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13872,32 +13872,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3909</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1766</t>
+          <t>2209</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8845</t>
+          <t>9272</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -13993,22 +13993,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>4351</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>1836</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7627</t>
+          <t>8904</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -14018,7 +14018,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -14028,22 +14028,22 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>4351</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>1836</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7627</t>
+          <t>8904</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -14053,7 +14053,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -14071,32 +14071,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>63974</t>
+          <t>69677</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>55684</t>
+          <t>60446</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>70506</t>
+          <t>77234</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -14106,32 +14106,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>63974</t>
+          <t>69677</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>55684</t>
+          <t>60446</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>70506</t>
+          <t>77234</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,28%</t>
         </is>
       </c>
     </row>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>7611</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>3150</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16563</t>
+          <t>18730</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -14184,22 +14184,22 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>7611</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>3150</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16563</t>
+          <t>18730</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -14209,7 +14209,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -14227,32 +14227,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>15559</t>
+          <t>17629</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10420</t>
+          <t>12097</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21626</t>
+          <t>24453</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -14262,32 +14262,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>15559</t>
+          <t>17629</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>10420</t>
+          <t>12097</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>21626</t>
+          <t>24453</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -14305,17 +14305,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>94279</t>
+          <t>103982</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>94279</t>
+          <t>103982</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>94279</t>
+          <t>103982</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -14340,17 +14340,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>94279</t>
+          <t>103982</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>94279</t>
+          <t>103982</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>94279</t>
+          <t>103982</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -14387,32 +14387,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>32383</t>
+          <t>36478</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23948</t>
+          <t>27000</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45675</t>
+          <t>48824</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14422,32 +14422,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>32383</t>
+          <t>36478</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>23948</t>
+          <t>27000</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>45675</t>
+          <t>48824</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -14465,32 +14465,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>4793</t>
+          <t>5767</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>2085</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11193</t>
+          <t>11792</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14500,32 +14500,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>4793</t>
+          <t>5767</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>2085</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11193</t>
+          <t>11792</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>6921</t>
+          <t>7606</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3716</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>11187</t>
+          <t>12521</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -14578,22 +14578,22 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6921</t>
+          <t>7606</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3716</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>11187</t>
+          <t>12521</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -14621,32 +14621,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>322548</t>
+          <t>359627</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>304857</t>
+          <t>340754</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>338285</t>
+          <t>375633</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14656,32 +14656,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>322548</t>
+          <t>359627</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>304857</t>
+          <t>340754</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>338285</t>
+          <t>375633</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>75,66%</t>
         </is>
       </c>
     </row>
@@ -14699,32 +14699,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>17297</t>
+          <t>19393</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11257</t>
+          <t>12247</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26770</t>
+          <t>29088</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14734,32 +14734,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>17297</t>
+          <t>19393</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>11257</t>
+          <t>12247</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>26770</t>
+          <t>29088</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -14777,32 +14777,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>60662</t>
+          <t>67593</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>49308</t>
+          <t>55012</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>74991</t>
+          <t>82102</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14812,32 +14812,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>60662</t>
+          <t>67593</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>49308</t>
+          <t>55012</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>74991</t>
+          <t>82102</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,54%</t>
         </is>
       </c>
     </row>
@@ -14855,17 +14855,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>444604</t>
+          <t>496463</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>444604</t>
+          <t>496463</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>444604</t>
+          <t>496463</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14890,17 +14890,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>444604</t>
+          <t>496463</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>444604</t>
+          <t>496463</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>444604</t>
+          <t>496463</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14937,32 +14937,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>37202</t>
+          <t>34999</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>23153</t>
+          <t>26628</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>56164</t>
+          <t>46482</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14972,32 +14972,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>37202</t>
+          <t>34999</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>23153</t>
+          <t>26628</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>56164</t>
+          <t>46482</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -15015,32 +15015,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2970</t>
+          <t>3212</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>6988</t>
+          <t>7405</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -15050,32 +15050,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>2970</t>
+          <t>3212</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>6988</t>
+          <t>7405</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -15093,32 +15093,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>22326</t>
+          <t>25036</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>14152</t>
+          <t>17715</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>32154</t>
+          <t>31974</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -15128,32 +15128,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>22326</t>
+          <t>25036</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>14152</t>
+          <t>17715</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>32154</t>
+          <t>31974</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -15171,32 +15171,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>346925</t>
+          <t>308896</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>285425</t>
+          <t>292463</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>409416</t>
+          <t>325292</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -15206,32 +15206,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>346925</t>
+          <t>308896</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>285425</t>
+          <t>292463</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>409416</t>
+          <t>325292</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>68,78%</t>
         </is>
       </c>
     </row>
@@ -15249,32 +15249,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>10999</t>
+          <t>11414</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5498</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>19176</t>
+          <t>20331</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -15284,32 +15284,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>10999</t>
+          <t>11414</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>5498</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>19176</t>
+          <t>20331</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -15327,32 +15327,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>112781</t>
+          <t>89387</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>75115</t>
+          <t>75648</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>202122</t>
+          <t>104293</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -15362,32 +15362,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>112781</t>
+          <t>89387</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>75115</t>
+          <t>75648</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>202122</t>
+          <t>104293</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>22,05%</t>
         </is>
       </c>
     </row>
@@ -15405,17 +15405,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>533202</t>
+          <t>472944</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>533202</t>
+          <t>472944</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>533202</t>
+          <t>472944</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -15440,17 +15440,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>533202</t>
+          <t>472944</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>533202</t>
+          <t>472944</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>533202</t>
+          <t>472944</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -15472,7 +15472,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -15487,32 +15487,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>24455</t>
+          <t>26587</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>16957</t>
+          <t>18231</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>36439</t>
+          <t>38775</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -15522,32 +15522,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>24455</t>
+          <t>26587</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>16957</t>
+          <t>18231</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>36439</t>
+          <t>38775</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -15565,7 +15565,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -15575,12 +15575,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>3692</t>
+          <t>4613</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -15590,7 +15590,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -15600,7 +15600,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -15610,12 +15610,12 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>3692</t>
+          <t>4613</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -15625,7 +15625,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -15643,32 +15643,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>24220</t>
+          <t>27033</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>17446</t>
+          <t>20052</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>31433</t>
+          <t>35352</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -15678,32 +15678,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>24220</t>
+          <t>27033</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>17446</t>
+          <t>20052</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>31433</t>
+          <t>35352</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -15721,32 +15721,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>250807</t>
+          <t>272906</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>234771</t>
+          <t>254851</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>266309</t>
+          <t>288763</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15756,32 +15756,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>250807</t>
+          <t>272906</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>234771</t>
+          <t>254851</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>266309</t>
+          <t>288763</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,25%</t>
         </is>
       </c>
     </row>
@@ -15799,32 +15799,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>7042</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>3928</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>11891</t>
+          <t>13903</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15834,32 +15834,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>7042</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3928</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>11891</t>
+          <t>13903</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -15877,32 +15877,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>74491</t>
+          <t>81204</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>62565</t>
+          <t>69407</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>87878</t>
+          <t>97656</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15912,32 +15912,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>74491</t>
+          <t>81204</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>62565</t>
+          <t>69407</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>87878</t>
+          <t>97656</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,42%</t>
         </is>
       </c>
     </row>
@@ -15955,17 +15955,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>382200</t>
+          <t>416967</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>382200</t>
+          <t>416967</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>382200</t>
+          <t>416967</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -15990,17 +15990,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>382200</t>
+          <t>416967</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>382200</t>
+          <t>416967</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>382200</t>
+          <t>416967</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -16037,32 +16037,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>119095</t>
+          <t>125869</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>98399</t>
+          <t>108453</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>147536</t>
+          <t>148837</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -16072,32 +16072,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>119095</t>
+          <t>125869</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>98399</t>
+          <t>108453</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>147536</t>
+          <t>148837</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -16115,32 +16115,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>11827</t>
+          <t>13343</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>7037</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>19532</t>
+          <t>21577</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -16150,32 +16150,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>11827</t>
+          <t>13343</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>7037</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>19532</t>
+          <t>21577</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -16193,32 +16193,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>64613</t>
+          <t>71741</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>52798</t>
+          <t>60825</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>77081</t>
+          <t>85698</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -16228,32 +16228,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>64613</t>
+          <t>71741</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>52798</t>
+          <t>60825</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>77081</t>
+          <t>85698</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -16271,32 +16271,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>1385026</t>
+          <t>1452593</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>1306913</t>
+          <t>1417271</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>1448460</t>
+          <t>1487546</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -16306,32 +16306,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>1385026</t>
+          <t>1452593</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>1306913</t>
+          <t>1417271</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>1448460</t>
+          <t>1487546</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>72,57%</t>
         </is>
       </c>
     </row>
@@ -16349,32 +16349,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>57698</t>
+          <t>62870</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>44062</t>
+          <t>48133</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>73971</t>
+          <t>78861</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -16384,32 +16384,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>57698</t>
+          <t>62870</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>44062</t>
+          <t>48133</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>73971</t>
+          <t>78861</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -16427,32 +16427,32 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>322575</t>
+          <t>323498</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>276692</t>
+          <t>297204</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>418654</t>
+          <t>355880</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -16462,32 +16462,32 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>322575</t>
+          <t>323498</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>276692</t>
+          <t>297204</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>418654</t>
+          <t>355880</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>17,36%</t>
         </is>
       </c>
     </row>
@@ -16505,17 +16505,17 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>1960834</t>
+          <t>2049912</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>1960834</t>
+          <t>2049912</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>1960834</t>
+          <t>2049912</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -16540,17 +16540,17 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>1960834</t>
+          <t>2049912</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>1960834</t>
+          <t>2049912</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1960834</t>
+          <t>2049912</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
